--- a/Result/checksun_type/隨身碟、記憶卡讀卡機.xlsx
+++ b/Result/checksun_type/隨身碟、記憶卡讀卡機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>1083.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>1161.0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>941.52</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>941.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>11044007.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>10310343.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>10310343.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>12189115.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7200103.34</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7200103.34</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>222676.295160234</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>11044007</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>11044007.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>1104.0</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>1162.5</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>932.94</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>1162.5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>932.9400000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>11514547.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>10718145.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>10718145.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>12093749.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7076429.1</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7076429.1</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>249857.6850912869</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>11514547</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>11514547.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>1123.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>1158.75</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>923.04</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>1158.75</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>923.04</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>9945798.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>10987468.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>10987468.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>12453475.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>6977252.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>6977252.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>229349.7533823866</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>9945798</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>9945798.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>1170.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>1154.4</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>912.94</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>1154.4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>912.9400000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2001625.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>11465158.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>11465158.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>12246347.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>6827329.64</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>6827329.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>359941.8954631593</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2001625</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2001625.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>1209.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1145.15</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>902.42</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>1145.15</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>902.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>17045741.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>13854763.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>13854763.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>13082235.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>6862520.38</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>6862520.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1384808.423597721</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>17045741</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>17045741.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>1236.0</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>1129.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>889.38</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>1129.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>889.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>13083016.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>14067887.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>14067887.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>12535839.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6585064.6</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>6585064.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1187576.448661461</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>13083016</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>13083016.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>1275.0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1117.0</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>876.59</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>876.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>12861162.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>13469353.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>13469353.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>12341879.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>6333215.78</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>6333215.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1287980.718443181</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>12861162</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>12861162.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>1298.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1100.0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>862.33</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>862.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>12334248.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>13919483.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>13919483</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>11755920.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>6082618.26</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>6082618.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1409186.149615526</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>12334248</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>12334248.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>1294.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>1078.0</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>846.13</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>1078</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>846.13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>13949649.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>13027535.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>13027535.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>11190906.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>5843639.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>5843639.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>1588463.760232607</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>13949649</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>13949649.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>1273.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>1058.0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>830.59</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>830.59</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>18111363.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>12309707.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>12309707.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>10554227.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>5575748.22</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>5575748.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1614765.105391558</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>18111363</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>18111363.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>1242.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>1031.35</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>814.07</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>1031.35</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>814.0700000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>10090347.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>11003791.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>11003791</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>10162691.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>5231041.08</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>5231041.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>1148770.34471179</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>10090347</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>10090347.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>97.72</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>105.26</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>93.04</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>105.26</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>93.04000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>823355183.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>828048160.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>828048160.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1225038029.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1324328785.42</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1324328785.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-173412215.8942757</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>823355183</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>823355183.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>98.74000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>105.69</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>92.41</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>105.69</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>92.41</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1258852726.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>809073241.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>809073241.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1561981535.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1310615220.32</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1310615220.32</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-160260284.3000026</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1258852726</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1258852726.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>100.14</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>105.84</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>91.69</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>105.84</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>91.69</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>433168332.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>840620629.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>840620629.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1980012303.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1288088836.48</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1288088836.48</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-182408680.0474694</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>433168332</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>433168332.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>103.06</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>106.87</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>91.08</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>91.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>600916916.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1290701738.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1290701738.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2232414586.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1281765152.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1281765152.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-119068464.6135838</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>600916916</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>600916916.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>106.7</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>107.56</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>90.47</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>90.47</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1023947646.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1352039170.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1352039170</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2374588560.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1277256806.58</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1277256806.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-42303059.97183347</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1023947646</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1023947646.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>109.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>107.86</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>89.73</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>107.86</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>89.73</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>728480586.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1622027898.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1622027898.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2380821510.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1262652823.74</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1262652823.74</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>23547906.30108953</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>728480586</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>728480586.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>114.0</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>108.28</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>88.96</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>108.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>88.95999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1416589666.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2314889830.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2314889830.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2383969407.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1249526901.34</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1249526901.34</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>148436903.608798</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1416589666</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1416589666.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>117.0</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>108.3</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>88.08</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2683573878.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3119403978.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>3119403978.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2360636845.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1223088359.32</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1223088359.32</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>247822466.0623529</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2683573878</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2683573878.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>118.5</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>108.53</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>87.13</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>108.53</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>87.13</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>907604074.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3174127434.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3174127434.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2117864802.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1170490061.88</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1170490061.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>245202730.2080615</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>907604074</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>907604074.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>116.9</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>108.46</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>86.09</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>108.46</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>86.09</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>2373891289.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>3397137951.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>3397137951.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2041969444.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1153464447.3</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1153464447.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>422985489.0516434</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2373891289</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2373891289.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>112.7</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>107.7</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>85.01</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>85.01000000000001</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>4192790244.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3139615121.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3139615121.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1822034797.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1107759800.68</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1107759800.68</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>504752032.6120589</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>4192790244</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>4192790244.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>40.13</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>43.51</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>41.98</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>41.98</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>106290.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>161293.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>161293.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>343614.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>783410.6</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>783410.6</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-172212.3280613442</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>106290</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>106290.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>40.53</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>43.79</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>41.95</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>41.95</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>168020.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>170723.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>170723.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>484046.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>794195.7</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>794195.7</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-170696.7208305846</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>168020</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>168020.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>41.0</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>44.11</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>41.87</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>41.87</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>113829.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>182532.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>182532.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>693516.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>837177.38</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>837177.38</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-169049.1847569787</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>113829</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>113829.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>42.25</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>44.55</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>41.87</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>41.87</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>156692.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>257000.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>257000.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1048293.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>868907.86</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>868907.86</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-154851.912339078</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>156692</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>156692.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>41.82</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>41.82</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>261636.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>309236.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>309236</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1157074.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>869617.98</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>869617.98</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-133632.133444253</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>261636</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>261636.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>44.73</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>45.05</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>41.64</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>41.64</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>153441.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>525936.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>525936.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1164150.1</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>870207.72</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>870207.72</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-109789.5874000653</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>153441</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>153441.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>46.39</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>41.42</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>227065.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>797370.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>797370.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1166240.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>867612.32</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>867612.3199999999</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-60215.4292155091</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>227065</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>227065.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>47.46</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>45.68</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>41.16</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>41.16</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>486169.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1204499.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1204499.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1167168.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>863369.54</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>863369.54</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>4867.062091553584</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>486169</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>486169.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>47.87</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>45.74</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>40.84</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>40.84</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>417869.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1839586.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1839586.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1141080.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>854060.12</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>854060.12</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>69907.08316980186</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>417869</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>417869.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>48.12</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>40.53</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>40.53</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1345137.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2004913.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2004913.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1122849.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>846276.3</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>846276.3</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>167642.5745969494</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1345137</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1345137.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>47.03</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>45.14</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>40.18</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>40.18</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1510611.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1802364.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1802364</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1038131.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>820502.94</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>820502.9399999999</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>201927.3275429835</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1510611</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1510611.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>33.89</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>34.8</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>33616.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>63736.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>63736.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>117904.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>192260.42</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>192260.42</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-36635.84465725953</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>33616</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>33616.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>34.71</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>34.64</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>34.64</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>43238.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>70440.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>70440</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>141996.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>191848.64</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>191848.64</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-34961.21443396773</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>43238</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>43238.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>35.6</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>34.48</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>34.48</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>42619.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>81501.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>81501.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>170054.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>191271.8</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>191271.8</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-32351.19931376635</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>42619</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>42619.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>37.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>37.55</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>34.32</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>34.32</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>75263.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>105273.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>105273.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>219996.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>190534.96</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>190534.96</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-27400.88488084415</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>75263</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>75263.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>38.04</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>37.67</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>34.16</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>34.16</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>123945.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>111056.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>111056.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>242178.9</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>189442.54</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>189442.54</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-22847.97551663945</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>123945</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>123945.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>38.89</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>37.67</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>33.95</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>33.95</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>67135.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>172072.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>172072.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>237020.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>187232.08</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>187232.08</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-20743.74872789561</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>67135</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>67135.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>39.46</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>37.65</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>98547.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>213552.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>213552.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>235694.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>185920.52</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>185920.52</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-10910.0765751224</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>98547</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>98547.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>39.53</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>37.54</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>33.41</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>33.41</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>161476.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>258606.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>258606.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>234775.1</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>183998.74</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>183998.74</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>162.1006636651291</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>161476</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>161476.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>39.35</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>37.39</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>33.09</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>33.09</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>104178.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>334720.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>334720.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>230114.4</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>180816.98</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>180816.98</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>9231.314552516385</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>104178</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>104178.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>39.15</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>37.38</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>32.8</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>429027.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>373301.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>373301.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>285831.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>178774.64</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>178774.64</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>27996.71601685695</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>429027</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>429027.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>38.36</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>37.21</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>32.49</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>274535.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>301968.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>301968.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>276797.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>170392.76</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>170392.76</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>18999.29967959854</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>274535</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>274535.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>128.7</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>136.95</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>117.98</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>136.95</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>117.98</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>685768948.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1204730015.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>1204730015.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1908935559.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1927133518.76</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1927133518.76</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-300336160.2296386</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>685768948</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>685768948.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>131.4</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>137.02</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>116.97</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>137.02</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>116.97</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>957412922.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1260779108.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1260779108.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>2274089229.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1920504823.04</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1920504823.04</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-249764348.8638506</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>957412922</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>957412922.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>133.5</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>136.93</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>115.78</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>136.93</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>115.78</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>657039345.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1423303697.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1423303697.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>2625148175.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1903379767.1</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1903379767.1</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-197703460.2390163</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>657039345</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>657039345.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>137.7</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>114.71</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>114.71</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1156415197.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>2082691015.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>2082691015.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>3102508393.6</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1895115467.4</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1895115467.4</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-84087041.08785963</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1156415197</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1156415197.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>141.0</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>137.6</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>113.69</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>137.6</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>113.69</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>2567013667.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>2208254208.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>2208254208</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>3292817162.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1878225233.76</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1878225233.76</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>27720682.16693115</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2567013667</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2567013667.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>143.7</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>137.25</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>112.51</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>112.51</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>966014411.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>2613141102.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>2613141102.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>3351697105.2</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1832573535.5</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1832573535.5</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>35320426.3820982</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>966014411</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>966014411.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>145.8</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>136.78</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>111.23</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>136.78</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>111.23</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1770035868.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>3287399350.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>3287399350.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>3455448617.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1814759134.9</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1814759134.9</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>216451394.6044049</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1770035868</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1770035868.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>145.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>136.05</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>109.84</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>136.05</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>109.84</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>3953975935.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>3826992654.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>3826992654</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>3493897061.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1780059536.34</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1780059536.34</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>381334357.5789719</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>3953975935</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>3953975935.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>145.9</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>135.12</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>108.37</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>135.12</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>108.37</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1784231159.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>4122325771.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>4122325771.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>3172927912.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1702406729.6</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1702406729.6</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>369268784.7362471</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1784231159</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1784231159.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>144.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>134.5</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>107.01</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>107.01</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>4591448141.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>4377380117.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>4377380117.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>3045153382.1</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1668781080.76</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1668781080.76</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>571316735.7917738</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>4591448141</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>4591448141.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>142.6</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>133.32</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>105.52</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>133.32</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>105.52</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>4337305650.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>4090253107.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>4090253107.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>2616515756.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1578952077.3</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1578952077.3</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>538779248.664249</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>4337305650</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>4337305650.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>217717</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>149413</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>216732</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>221658</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>301588</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>199194</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>216632</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>357016</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>609988</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>600689</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>797538</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>321219</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>681031</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>12.21</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>13.46</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>13.46</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>2237.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1738.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1738.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>2390.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>4157.88</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>4157.88</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-293.7660102395739</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>2237</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>2237.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>12.12</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>12.72</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>13.49</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>13.49</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>2287.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1763.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1763.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>2734.6</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>4238.28</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>4238.28</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-333.0583208832609</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>2287</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>2287.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>12.11</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>12.77</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>13.53</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>13.53</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>976.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1758.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1758.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>2799.0</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>4265.64</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>4265.64</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-382.652396056983</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>976</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>976.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>12.22</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>12.84</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>13.58</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>13.58</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1820.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>2289.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>2289.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>3028.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>4305.5</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>4305.5</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-299.3706321602649</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1820</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1820.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>12.41</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>12.94</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>13.63</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>13.63</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>1371.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>2355.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>2355</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3008.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>4324.54</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>4324.54</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-260.1334468735158</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1371</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1371.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>12.59</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>13.02</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>13.67</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>13.67</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>2364.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>3043.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>3043</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>3522.1</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>4362.96</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>4362.96</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-146.6827019326774</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>2364</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>2364.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>12.82</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>13.72</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>13.72</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>2263.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>3705.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>3705.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>3571.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>4398.72</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>4398.72</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-85.76439837674116</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>2263</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>2263.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>12.98</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>13.76</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>13.76</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>3631.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>3839.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>3839.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>3609.2</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>4461.92</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>4461.92</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>15.14619235948066</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>3631</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>3631.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>13.08</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>13.23</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>13.79</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>13.79</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>2146.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>3767.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>3767.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3510.4</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>4475.36</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>4475.36</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>12.19181511267243</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>2146</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>2146.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>13.13</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>13.26</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>13.82</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>13.82</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>4811.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>3661.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>3661</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>3534.0</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>4696.48</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>4696.48</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>166.6429970774943</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>4811</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>4811.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>13.15</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>13.28</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>13.86</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>5677.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>4001.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>4001.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>3431.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>6309.52</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>6309.52</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>95.80029284590046</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>5677</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>5677.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>18.99</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>22.56</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>513.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>481.6</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>481.6</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>955.5</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>945.86</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>945.86</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-112.0936968119468</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>513</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>513.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>18.96</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>20.84</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>22.66</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>22.66</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>686.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>652.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>652.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1027.3</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>962.3</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>962.3</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-102.1091227620544</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>686</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>686.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>19.05</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>22.76</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>22.76</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>278.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>766.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>766.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1078.8</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>965.32</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>965.3200000000001</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-102.7344054492778</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>278</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>19.18</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>21.28</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>22.86</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>457.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>999.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>999.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1199.3</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>989.86</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>989.86</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-56.24429480783692</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>457</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>457.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>19.53</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>22.97</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>474.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1017.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1017</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1218.1</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1011.94</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1011.94</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-6.999697648355777</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>474</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>474.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>19.93</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>23.08</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>23.08</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>1367.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1429.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1429.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1250.2</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1013.74</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1013.74</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>61.77828749548712</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1367</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1367.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>20.33</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>22.03</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>23.2</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>1256.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1402.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1402.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1286.0</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1006.36</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1006.36</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>62.14761314756674</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1256</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1256.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>20.61</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>22.24</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>23.29</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1444.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1391.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1391.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1259.2</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>991.4</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>991.4</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>72.3485207524102</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1444</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1444.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>20.86</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>22.44</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>544.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1399.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1399</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1179.6</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>984.14</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>984.14</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>64.1945130181723</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>544</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>21.06</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>23.46</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>23.46</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>2536.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1419.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1419.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1185.4</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>984.76</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>984.76</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>146.6818407900403</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>2536</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>2536.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>21.2</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>23.52</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>23.52</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>1231.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1071.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1071</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1030.5</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>962.14</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>962.14</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>45.85367186449298</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>1231</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>1231.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>179.1</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>195.32</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>177.22</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>195.32</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>177.22</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>1623779.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>2574301.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>2574301.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>3436834.9</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>0</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-421128.8502966315</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>1623779</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>1623779.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>182.4</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>196.08</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>176.06</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>176.06</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>3062446.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>2775498.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>2775498.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>3970142.1</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>0</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-335506.8946805983</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>3062446</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>3062446.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>187.1</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>196.72</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>174.83</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>196.72</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>174.83</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>1610839.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>2702183.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>2702183</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>4205293.9</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>0</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-355350.318990529</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>1610839</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>1610839.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>193.0</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>198.05</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>173.52</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>198.05</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>173.52</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>3054769.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>3357085.6</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>3357085.6</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>4763871.1</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>0</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-215477.6637550541</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>3054769</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>3054769.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>201.0</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>198.7</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>172.27</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>198.7</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>172.27</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>3519674.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>3331525.6</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>3331525.6</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>4695394.0</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>0</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-162670.739713124</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>3519674</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>3519674.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>207.0</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>198.22</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>170.66</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>198.22</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>170.66</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>2629766.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>4299368.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>4299368.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>4613187.1</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>0</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-131233.857520612</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>2629766</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>2629766.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>213.1</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>168.94</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>168.94</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>2695867.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>5164785.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>5164785.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>4603311.3</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>0</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>13710.18338014092</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>2695867</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>2695867.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>213.2</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>197.02</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>166.97</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>197.02</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>166.97</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>4885352.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>5708404.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>5708404.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>4713061.1</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>0</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>213201.1995462123</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>4885352</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>4885352.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>212.6</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>196.02</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>164.82</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>196.02</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>164.82</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>2926969.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>6170656.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>6170656.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>4449683.9</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>0</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>255986.358371092</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>2926969</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>2926969.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>208.9</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>194.78</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>162.57</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>194.78</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>162.57</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>8358888.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>6059262.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>6059262.4</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>4418644.6</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>0</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>517792.3938933816</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>8358888</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>8358888.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>203.3</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>192.88</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>160.21</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>192.88</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>160.21</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>6956851.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>4927005.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>4927005.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>4265532.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>0</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>291317.1091433177</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>6956851</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>6956851.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>35.56</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>35.92</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>33.84</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>27843591.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>45847539.4</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>45847539.4</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>239854872.8</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>76016911.16</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>76016911.16</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-22940622.92396608</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>27843591</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>27843591.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>35.46</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>33.75</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>41595329.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>55300192.0</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>55300192</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>264402531.1</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>75871454.36</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>75871454.36</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-17232914.85534656</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>41595329</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>41595329.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>35.5</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>35.89</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>35.89</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>33.67</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>38028960.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>69548306.0</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>69548306</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>269906804.1</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>75152003.64</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>75152003.64</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-9936985.441056281</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>38028960</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>38028960.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>35.69</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>35.85</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>33.58</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>33.58</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>47738287.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>131800479.8</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>131800479.8</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>276846407.0</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>74615229.88</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>74615229.88</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>1222774.166539013</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>47738287</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>47738287.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>36.48</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>35.78</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>33.51</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>33.51</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>74031530.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>216557750.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>216557750.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>276008619.1</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>73741737.0</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>73741737</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>16081332.35001302</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>74031530</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>74031530.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>37.45</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>35.65</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>33.41</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>33.41</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>75106854.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>433862206.2</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>433862206.2</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>271073722.7</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>72345427.86</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>72345427.86</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>33916377.56390396</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>75106854</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>75106854.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>37.86</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>33.33</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>112835899.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>473504870.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>473504870.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>264748728.2</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>70950980.6</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>70950980.59999999</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>58068501.09932303</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>112835899</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>112835899.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>37.86</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>35.44</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>33.24</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>349289829.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>470265302.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>470265302.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>258856335.9</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>68769109.22</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>68769109.22</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>86455262.00351733</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>349289829</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>349289829.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>37.76000000000001</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>33.13</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>33.13</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>471524641.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>421892334.2</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>421892334.2</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>229629785.8</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>61898002.48</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>61898002.48</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>98585740.00938356</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>471524641</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>471524641.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>36.98</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>32.96</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>35</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>32.96</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>1160553808.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>335459487.6</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>335459487.6</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>184363457.6</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>52651860.56</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>52651860.56</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>99297488.01742876</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>1160553808</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>1160553808.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>35.75</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>34.64</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>32.77</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>32.77</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>273320174.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>108285239.2</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>108285239.2</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>74733807.4</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>29618734.48</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>29618734.48</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>22943378.42115659</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>273320174</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>273320174.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>189.4</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>172.05</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>141.9</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>141.9</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>397311342.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>445456376.8</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>445456376.8</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>875166690.0</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>628820751.82</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>628820751.8200001</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-96400566.63131046</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>397311342</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>397311342.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>193.7</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>169.62</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>140.45</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>169.62</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>140.45</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>294101570.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>507364470.8</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>507364470.8</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>1144000736.3</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>625161567.52</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>625161567.52</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-85360955.75727904</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>294101570</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>294101570.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>195.9</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>166.78</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>138.86</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>166.78</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>138.86</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>304935356.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>601330334.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>601330334</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>1150164860.3</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>623185237.34</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>623185237.34</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-55483287.66018844</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>304935356</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>304935356.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>198.4</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>164.3</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>137.31</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>137.31</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>503846898.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>655775452.4</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>655775452.4</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>1168300793.6</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>621462145.82</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>621462145.8200001</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-11980121.46219528</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>503846898</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>503846898.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>200.3</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>161.52</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>135.71</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>161.52</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>135.71</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>727086718.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>800318914.8</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>800318914.8</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>1270783756.8</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>617166282.66</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>617166282.66</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>29283169.37287343</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>727086718</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>727086718.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>203.1</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>157.95</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>133.76</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>157.95</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>133.76</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>706851812.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>1304877003.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>1304877003.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>1231274265.4</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>605865630.64</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>605865630.64</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>63266348.08822608</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>706851812</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>706851812.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>201.5</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>154.3</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>131.7</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>131.7</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>763930886.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>1780637001.8</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>1780637001.8</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>1192911399.0</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>594452768.1</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>594452768.1</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>111722259.4641504</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>763930886</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>763930886.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>197.3</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>150.85</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>129.71</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>150.85</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>129.71</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>577160948.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>1698999386.6</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>1698999386.6</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>1146577241.5</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>580672214.04</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>580672214.04</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>170839294.2346084</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>577160948</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>577160948.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>190.1</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>147.55</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>127.72</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>147.55</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>127.72</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>1226564210.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>1680826134.8</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>1680826134.8</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>1118336266.4</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>570747347.3</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>570747347.3</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>269201862.4697411</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>1226564210</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>1226564210.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>180.6</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>144.72</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>125.78</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>144.72</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>125.78</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>3249877160.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>1741248598.8</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>1741248598.8</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>1020966896.2</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>547934421.98</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>547934421.98</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>330526543.9317255</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>3249877160</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>3249877160.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>164.4</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>140.28</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>123.48</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>140.28</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>123.48</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>3085651805.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>1157671527.6</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>1157671527.6</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>742202205.2</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>485151391.32</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>485151391.32</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>189545181.9512849</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>3085651805</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>3085651805.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>2251806679</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>2303990317</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>4282414081</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>3277325446</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>2111926901</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>2504000596</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>6330911536</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>3971577357</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>2253776059</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>3252501668</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>3950855603</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
